--- a/temas/Evaluación FWS PAN V2.xlsx
+++ b/temas/Evaluación FWS PAN V2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\Empresa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\Empresa\temas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D653B97C-75B8-4B21-947E-E2F3A2C2679D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFEE334-CD05-421B-B927-4C8156FDF4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AAA0FAA8-7E95-4682-84AD-E72BFF2457AF}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{AAA0FAA8-7E95-4682-84AD-E72BFF2457AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluación firewalls PAN" sheetId="1" r:id="rId1"/>
@@ -518,7 +518,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3373" uniqueCount="1645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3427" uniqueCount="1651">
   <si>
     <t>NUM</t>
   </si>
@@ -5632,6 +5632,24 @@
   </si>
   <si>
     <t>Imagen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generación, realiza inspección de trafico basado en? </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> realiza inspección de trafico basado en? </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> inspección de trafico basado en? </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> de trafico basado en? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">basado en? </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> nueva generación</t>
   </si>
 </sst>
 </file>
@@ -6156,14 +6174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00FB712E-D91E-49B2-834F-B9B4297D66B1}" name="Tabla4" displayName="Tabla4" ref="A1:L391" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
-  <autoFilter ref="A1:L391" xr:uid="{643E3B4F-A0E8-4F62-B469-F412113F7871}">
-    <filterColumn colId="11">
-      <filters>
-        <filter val="Nivel 1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00FB712E-D91E-49B2-834F-B9B4297D66B1}" name="Tabla4" displayName="Tabla4" ref="A1:L397" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
+  <autoFilter ref="A1:L397" xr:uid="{643E3B4F-A0E8-4F62-B469-F412113F7871}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J60">
     <sortCondition ref="A1:A60"/>
   </sortState>
@@ -6502,7 +6514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FABB11E8-A8CB-4FE8-A115-C34F16A49AEF}">
-  <dimension ref="A1:M391"/>
+  <dimension ref="A1:M397"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" style="7" bestFit="1" customWidth="1"/>
@@ -6558,7 +6570,7 @@
       </c>
       <c r="M1"/>
     </row>
-    <row r="2" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -6597,7 +6609,7 @@
       </c>
       <c r="M2"/>
     </row>
-    <row r="3" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -6633,7 +6645,7 @@
       </c>
       <c r="M3"/>
     </row>
-    <row r="4" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -6666,7 +6678,7 @@
       </c>
       <c r="M4"/>
     </row>
-    <row r="5" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -6702,7 +6714,7 @@
       </c>
       <c r="M5"/>
     </row>
-    <row r="6" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -6735,7 +6747,7 @@
       </c>
       <c r="M6"/>
     </row>
-    <row r="7" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -6768,7 +6780,7 @@
       </c>
       <c r="M7"/>
     </row>
-    <row r="8" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -6801,7 +6813,7 @@
       </c>
       <c r="M8"/>
     </row>
-    <row r="9" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -6837,7 +6849,7 @@
       </c>
       <c r="M9"/>
     </row>
-    <row r="10" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -6870,7 +6882,7 @@
       </c>
       <c r="M10"/>
     </row>
-    <row r="11" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -6903,7 +6915,7 @@
       </c>
       <c r="M11"/>
     </row>
-    <row r="12" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -6939,7 +6951,7 @@
       </c>
       <c r="M12"/>
     </row>
-    <row r="13" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -6975,7 +6987,7 @@
       </c>
       <c r="M13"/>
     </row>
-    <row r="14" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -7008,7 +7020,7 @@
       </c>
       <c r="M14"/>
     </row>
-    <row r="15" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -7041,7 +7053,7 @@
       </c>
       <c r="M15"/>
     </row>
-    <row r="16" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -7071,7 +7083,7 @@
       </c>
       <c r="M16"/>
     </row>
-    <row r="17" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -7107,7 +7119,7 @@
       </c>
       <c r="M17"/>
     </row>
-    <row r="18" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -7143,7 +7155,7 @@
       </c>
       <c r="M18"/>
     </row>
-    <row r="19" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -7176,7 +7188,7 @@
       </c>
       <c r="M19"/>
     </row>
-    <row r="20" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>19</v>
       </c>
@@ -7209,7 +7221,7 @@
       </c>
       <c r="M20"/>
     </row>
-    <row r="21" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -7242,7 +7254,7 @@
       </c>
       <c r="M21"/>
     </row>
-    <row r="22" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>21</v>
       </c>
@@ -7275,7 +7287,7 @@
       </c>
       <c r="M22"/>
     </row>
-    <row r="23" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -7308,7 +7320,7 @@
       </c>
       <c r="M23"/>
     </row>
-    <row r="24" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -7341,7 +7353,7 @@
       </c>
       <c r="M24"/>
     </row>
-    <row r="25" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -7377,7 +7389,7 @@
       </c>
       <c r="M25"/>
     </row>
-    <row r="26" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>25</v>
       </c>
@@ -7413,7 +7425,7 @@
       </c>
       <c r="M26"/>
     </row>
-    <row r="27" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -7449,7 +7461,7 @@
       </c>
       <c r="M27"/>
     </row>
-    <row r="28" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>27</v>
       </c>
@@ -7485,7 +7497,7 @@
       </c>
       <c r="M28"/>
     </row>
-    <row r="29" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>28</v>
       </c>
@@ -7518,7 +7530,7 @@
       </c>
       <c r="M29"/>
     </row>
-    <row r="30" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>29</v>
       </c>
@@ -7554,7 +7566,7 @@
       </c>
       <c r="M30"/>
     </row>
-    <row r="31" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>30</v>
       </c>
@@ -7587,7 +7599,7 @@
       </c>
       <c r="M31"/>
     </row>
-    <row r="32" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>31</v>
       </c>
@@ -7620,7 +7632,7 @@
       </c>
       <c r="M32"/>
     </row>
-    <row r="33" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -7656,7 +7668,7 @@
       </c>
       <c r="M33"/>
     </row>
-    <row r="34" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>33</v>
       </c>
@@ -7692,7 +7704,7 @@
       </c>
       <c r="M34"/>
     </row>
-    <row r="35" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -7725,7 +7737,7 @@
       </c>
       <c r="M35"/>
     </row>
-    <row r="36" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>35</v>
       </c>
@@ -7758,7 +7770,7 @@
       </c>
       <c r="M36"/>
     </row>
-    <row r="37" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>36</v>
       </c>
@@ -7791,7 +7803,7 @@
       </c>
       <c r="M37"/>
     </row>
-    <row r="38" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>37</v>
       </c>
@@ -7827,7 +7839,7 @@
       </c>
       <c r="M38"/>
     </row>
-    <row r="39" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>38</v>
       </c>
@@ -7863,7 +7875,7 @@
       </c>
       <c r="M39"/>
     </row>
-    <row r="40" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>39</v>
       </c>
@@ -7899,7 +7911,7 @@
       </c>
       <c r="M40"/>
     </row>
-    <row r="41" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>40</v>
       </c>
@@ -7935,7 +7947,7 @@
       </c>
       <c r="M41"/>
     </row>
-    <row r="42" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>41</v>
       </c>
@@ -7974,7 +7986,7 @@
       </c>
       <c r="M42"/>
     </row>
-    <row r="43" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>42</v>
       </c>
@@ -8007,7 +8019,7 @@
       </c>
       <c r="M43"/>
     </row>
-    <row r="44" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43</v>
       </c>
@@ -8043,7 +8055,7 @@
       </c>
       <c r="M44"/>
     </row>
-    <row r="45" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>44</v>
       </c>
@@ -8076,7 +8088,7 @@
       </c>
       <c r="M45"/>
     </row>
-    <row r="46" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>45</v>
       </c>
@@ -8112,7 +8124,7 @@
       </c>
       <c r="M46"/>
     </row>
-    <row r="47" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>46</v>
       </c>
@@ -8145,7 +8157,7 @@
       </c>
       <c r="M47"/>
     </row>
-    <row r="48" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>47</v>
       </c>
@@ -8178,7 +8190,7 @@
       </c>
       <c r="M48"/>
     </row>
-    <row r="49" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>48</v>
       </c>
@@ -8211,7 +8223,7 @@
       </c>
       <c r="M49"/>
     </row>
-    <row r="50" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>49</v>
       </c>
@@ -8244,7 +8256,7 @@
       </c>
       <c r="M50"/>
     </row>
-    <row r="51" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>50</v>
       </c>
@@ -8280,7 +8292,7 @@
       </c>
       <c r="M51"/>
     </row>
-    <row r="52" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>51</v>
       </c>
@@ -8313,7 +8325,7 @@
       </c>
       <c r="M52"/>
     </row>
-    <row r="53" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>52</v>
       </c>
@@ -8346,7 +8358,7 @@
       </c>
       <c r="M53"/>
     </row>
-    <row r="54" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>53</v>
       </c>
@@ -8382,7 +8394,7 @@
       </c>
       <c r="M54"/>
     </row>
-    <row r="55" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>54</v>
       </c>
@@ -8415,7 +8427,7 @@
       </c>
       <c r="M55"/>
     </row>
-    <row r="56" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>55</v>
       </c>
@@ -8448,7 +8460,7 @@
       </c>
       <c r="M56"/>
     </row>
-    <row r="57" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>56</v>
       </c>
@@ -8484,7 +8496,7 @@
       </c>
       <c r="M57"/>
     </row>
-    <row r="58" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>57</v>
       </c>
@@ -8517,7 +8529,7 @@
       </c>
       <c r="M58"/>
     </row>
-    <row r="59" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>58</v>
       </c>
@@ -8550,7 +8562,7 @@
       </c>
       <c r="M59"/>
     </row>
-    <row r="60" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>59</v>
       </c>
@@ -8583,7 +8595,7 @@
       </c>
       <c r="M60"/>
     </row>
-    <row r="61" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>60</v>
       </c>
@@ -8619,7 +8631,7 @@
       </c>
       <c r="M61"/>
     </row>
-    <row r="62" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>61</v>
       </c>
@@ -8652,7 +8664,7 @@
       </c>
       <c r="M62"/>
     </row>
-    <row r="63" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>62</v>
       </c>
@@ -8691,7 +8703,7 @@
       </c>
       <c r="M63"/>
     </row>
-    <row r="64" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>63</v>
       </c>
@@ -8727,7 +8739,7 @@
       </c>
       <c r="M64"/>
     </row>
-    <row r="65" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>64</v>
       </c>
@@ -8760,7 +8772,7 @@
       </c>
       <c r="M65"/>
     </row>
-    <row r="66" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>65</v>
       </c>
@@ -8793,7 +8805,7 @@
       </c>
       <c r="M66"/>
     </row>
-    <row r="67" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>66</v>
       </c>
@@ -8826,7 +8838,7 @@
       </c>
       <c r="M67"/>
     </row>
-    <row r="68" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>67</v>
       </c>
@@ -8859,7 +8871,7 @@
       </c>
       <c r="M68"/>
     </row>
-    <row r="69" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>68</v>
       </c>
@@ -8892,7 +8904,7 @@
       </c>
       <c r="M69"/>
     </row>
-    <row r="70" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>69</v>
       </c>
@@ -8925,7 +8937,7 @@
       </c>
       <c r="M70"/>
     </row>
-    <row r="71" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>70</v>
       </c>
@@ -8958,7 +8970,7 @@
       </c>
       <c r="M71"/>
     </row>
-    <row r="72" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>71</v>
       </c>
@@ -8994,7 +9006,7 @@
       </c>
       <c r="M72"/>
     </row>
-    <row r="73" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>72</v>
       </c>
@@ -9027,7 +9039,7 @@
       </c>
       <c r="M73"/>
     </row>
-    <row r="74" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>73</v>
       </c>
@@ -9060,7 +9072,7 @@
       </c>
       <c r="M74"/>
     </row>
-    <row r="75" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>74</v>
       </c>
@@ -9093,7 +9105,7 @@
       </c>
       <c r="M75"/>
     </row>
-    <row r="76" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>75</v>
       </c>
@@ -9126,7 +9138,7 @@
       </c>
       <c r="M76"/>
     </row>
-    <row r="77" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>76</v>
       </c>
@@ -9159,7 +9171,7 @@
       </c>
       <c r="M77"/>
     </row>
-    <row r="78" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>77</v>
       </c>
@@ -9192,7 +9204,7 @@
       </c>
       <c r="M78"/>
     </row>
-    <row r="79" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>78</v>
       </c>
@@ -9225,7 +9237,7 @@
       </c>
       <c r="M79"/>
     </row>
-    <row r="80" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>79</v>
       </c>
@@ -9258,7 +9270,7 @@
       </c>
       <c r="M80"/>
     </row>
-    <row r="81" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>80</v>
       </c>
@@ -9291,7 +9303,7 @@
       </c>
       <c r="M81"/>
     </row>
-    <row r="82" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>81</v>
       </c>
@@ -9327,7 +9339,7 @@
       </c>
       <c r="M82"/>
     </row>
-    <row r="83" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>82</v>
       </c>
@@ -9360,7 +9372,7 @@
       </c>
       <c r="M83"/>
     </row>
-    <row r="84" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>83</v>
       </c>
@@ -9396,7 +9408,7 @@
       </c>
       <c r="M84"/>
     </row>
-    <row r="85" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>84</v>
       </c>
@@ -9432,7 +9444,7 @@
       </c>
       <c r="M85"/>
     </row>
-    <row r="86" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>85</v>
       </c>
@@ -9465,7 +9477,7 @@
       </c>
       <c r="M86"/>
     </row>
-    <row r="87" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>86</v>
       </c>
@@ -9498,7 +9510,7 @@
       </c>
       <c r="M87"/>
     </row>
-    <row r="88" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>87</v>
       </c>
@@ -9531,7 +9543,7 @@
       </c>
       <c r="M88"/>
     </row>
-    <row r="89" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>88</v>
       </c>
@@ -9564,7 +9576,7 @@
       </c>
       <c r="M89"/>
     </row>
-    <row r="90" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>89</v>
       </c>
@@ -9597,7 +9609,7 @@
       </c>
       <c r="M90"/>
     </row>
-    <row r="91" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>90</v>
       </c>
@@ -9630,7 +9642,7 @@
       </c>
       <c r="M91"/>
     </row>
-    <row r="92" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>91</v>
       </c>
@@ -9663,7 +9675,7 @@
       </c>
       <c r="M92"/>
     </row>
-    <row r="93" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>92</v>
       </c>
@@ -9696,7 +9708,7 @@
       </c>
       <c r="M93"/>
     </row>
-    <row r="94" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>93</v>
       </c>
@@ -9729,7 +9741,7 @@
       </c>
       <c r="M94"/>
     </row>
-    <row r="95" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>94</v>
       </c>
@@ -9762,7 +9774,7 @@
       </c>
       <c r="M95"/>
     </row>
-    <row r="96" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>95</v>
       </c>
@@ -9798,7 +9810,7 @@
       </c>
       <c r="M96"/>
     </row>
-    <row r="97" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>96</v>
       </c>
@@ -9831,7 +9843,7 @@
       </c>
       <c r="M97"/>
     </row>
-    <row r="98" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>97</v>
       </c>
@@ -9864,7 +9876,7 @@
       </c>
       <c r="M98"/>
     </row>
-    <row r="99" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>98</v>
       </c>
@@ -9897,7 +9909,7 @@
       </c>
       <c r="M99"/>
     </row>
-    <row r="100" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>99</v>
       </c>
@@ -9930,7 +9942,7 @@
       </c>
       <c r="M100"/>
     </row>
-    <row r="101" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>100</v>
       </c>
@@ -9963,7 +9975,7 @@
       </c>
       <c r="M101"/>
     </row>
-    <row r="102" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>101</v>
       </c>
@@ -9999,7 +10011,7 @@
       </c>
       <c r="M102"/>
     </row>
-    <row r="103" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>102</v>
       </c>
@@ -10032,7 +10044,7 @@
       </c>
       <c r="M103"/>
     </row>
-    <row r="104" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>103</v>
       </c>
@@ -10065,7 +10077,7 @@
       </c>
       <c r="M104"/>
     </row>
-    <row r="105" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>104</v>
       </c>
@@ -10098,7 +10110,7 @@
       </c>
       <c r="M105"/>
     </row>
-    <row r="106" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>105</v>
       </c>
@@ -10131,7 +10143,7 @@
       </c>
       <c r="M106"/>
     </row>
-    <row r="107" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>106</v>
       </c>
@@ -10164,7 +10176,7 @@
       </c>
       <c r="M107"/>
     </row>
-    <row r="108" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>107</v>
       </c>
@@ -10197,7 +10209,7 @@
       </c>
       <c r="M108"/>
     </row>
-    <row r="109" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>108</v>
       </c>
@@ -10230,7 +10242,7 @@
       </c>
       <c r="M109"/>
     </row>
-    <row r="110" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>109</v>
       </c>
@@ -10266,7 +10278,7 @@
       </c>
       <c r="M110"/>
     </row>
-    <row r="111" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>110</v>
       </c>
@@ -10299,7 +10311,7 @@
       </c>
       <c r="M111"/>
     </row>
-    <row r="112" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>111</v>
       </c>
@@ -10332,7 +10344,7 @@
       </c>
       <c r="M112"/>
     </row>
-    <row r="113" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>112</v>
       </c>
@@ -10365,7 +10377,7 @@
       </c>
       <c r="M113"/>
     </row>
-    <row r="114" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>113</v>
       </c>
@@ -10398,7 +10410,7 @@
       </c>
       <c r="M114"/>
     </row>
-    <row r="115" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>114</v>
       </c>
@@ -10431,7 +10443,7 @@
       </c>
       <c r="M115"/>
     </row>
-    <row r="116" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>115</v>
       </c>
@@ -10464,7 +10476,7 @@
       </c>
       <c r="M116"/>
     </row>
-    <row r="117" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>116</v>
       </c>
@@ -10497,7 +10509,7 @@
       </c>
       <c r="M117"/>
     </row>
-    <row r="118" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>117</v>
       </c>
@@ -10530,7 +10542,7 @@
       </c>
       <c r="M118"/>
     </row>
-    <row r="119" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>118</v>
       </c>
@@ -10563,7 +10575,7 @@
       </c>
       <c r="M119"/>
     </row>
-    <row r="120" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>119</v>
       </c>
@@ -10596,7 +10608,7 @@
       </c>
       <c r="M120"/>
     </row>
-    <row r="121" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>120</v>
       </c>
@@ -10629,7 +10641,7 @@
       </c>
       <c r="M121"/>
     </row>
-    <row r="122" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>121</v>
       </c>
@@ -10662,7 +10674,7 @@
       </c>
       <c r="M122"/>
     </row>
-    <row r="123" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>122</v>
       </c>
@@ -10695,7 +10707,7 @@
       </c>
       <c r="M123"/>
     </row>
-    <row r="124" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>123</v>
       </c>
@@ -10731,7 +10743,7 @@
       </c>
       <c r="M124"/>
     </row>
-    <row r="125" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>124</v>
       </c>
@@ -10764,7 +10776,7 @@
       </c>
       <c r="M125"/>
     </row>
-    <row r="126" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>125</v>
       </c>
@@ -10797,7 +10809,7 @@
       </c>
       <c r="M126"/>
     </row>
-    <row r="127" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>126</v>
       </c>
@@ -10833,7 +10845,7 @@
       </c>
       <c r="M127"/>
     </row>
-    <row r="128" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>127</v>
       </c>
@@ -10866,7 +10878,7 @@
       </c>
       <c r="M128"/>
     </row>
-    <row r="129" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>128</v>
       </c>
@@ -10902,7 +10914,7 @@
       </c>
       <c r="M129"/>
     </row>
-    <row r="130" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>129</v>
       </c>
@@ -10935,7 +10947,7 @@
       </c>
       <c r="M130"/>
     </row>
-    <row r="131" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>130</v>
       </c>
@@ -10968,7 +10980,7 @@
       </c>
       <c r="M131"/>
     </row>
-    <row r="132" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>131</v>
       </c>
@@ -11001,7 +11013,7 @@
       </c>
       <c r="M132"/>
     </row>
-    <row r="133" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>132</v>
       </c>
@@ -11034,7 +11046,7 @@
       </c>
       <c r="M133"/>
     </row>
-    <row r="134" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>133</v>
       </c>
@@ -11067,7 +11079,7 @@
       </c>
       <c r="M134"/>
     </row>
-    <row r="135" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>134</v>
       </c>
@@ -11103,7 +11115,7 @@
       </c>
       <c r="M135"/>
     </row>
-    <row r="136" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>135</v>
       </c>
@@ -11139,7 +11151,7 @@
       </c>
       <c r="M136"/>
     </row>
-    <row r="137" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>136</v>
       </c>
@@ -11172,7 +11184,7 @@
       </c>
       <c r="M137"/>
     </row>
-    <row r="138" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>137</v>
       </c>
@@ -11205,7 +11217,7 @@
       </c>
       <c r="M138"/>
     </row>
-    <row r="139" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>138</v>
       </c>
@@ -11238,7 +11250,7 @@
       </c>
       <c r="M139"/>
     </row>
-    <row r="140" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>139</v>
       </c>
@@ -11271,7 +11283,7 @@
       </c>
       <c r="M140"/>
     </row>
-    <row r="141" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>140</v>
       </c>
@@ -11307,7 +11319,7 @@
       </c>
       <c r="M141"/>
     </row>
-    <row r="142" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>141</v>
       </c>
@@ -11343,7 +11355,7 @@
       </c>
       <c r="M142"/>
     </row>
-    <row r="143" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>142</v>
       </c>
@@ -11379,7 +11391,7 @@
       </c>
       <c r="M143"/>
     </row>
-    <row r="144" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>143</v>
       </c>
@@ -11412,7 +11424,7 @@
       </c>
       <c r="M144"/>
     </row>
-    <row r="145" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>144</v>
       </c>
@@ -11445,7 +11457,7 @@
       </c>
       <c r="M145"/>
     </row>
-    <row r="146" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>145</v>
       </c>
@@ -11478,7 +11490,7 @@
       </c>
       <c r="M146"/>
     </row>
-    <row r="147" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>146</v>
       </c>
@@ -11514,7 +11526,7 @@
       </c>
       <c r="M147"/>
     </row>
-    <row r="148" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>147</v>
       </c>
@@ -11547,7 +11559,7 @@
       </c>
       <c r="M148"/>
     </row>
-    <row r="149" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>148</v>
       </c>
@@ -11580,7 +11592,7 @@
       </c>
       <c r="M149"/>
     </row>
-    <row r="150" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>149</v>
       </c>
@@ -11613,7 +11625,7 @@
       </c>
       <c r="M150"/>
     </row>
-    <row r="151" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>150</v>
       </c>
@@ -11648,7 +11660,7 @@
       </c>
       <c r="M151"/>
     </row>
-    <row r="152" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>151</v>
       </c>
@@ -11683,7 +11695,7 @@
       </c>
       <c r="M152"/>
     </row>
-    <row r="153" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>152</v>
       </c>
@@ -11720,7 +11732,7 @@
       </c>
       <c r="M153"/>
     </row>
-    <row r="154" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>153</v>
       </c>
@@ -11755,7 +11767,7 @@
       </c>
       <c r="M154"/>
     </row>
-    <row r="155" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>154</v>
       </c>
@@ -11790,7 +11802,7 @@
       </c>
       <c r="M155"/>
     </row>
-    <row r="156" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>155</v>
       </c>
@@ -11825,7 +11837,7 @@
       </c>
       <c r="M156"/>
     </row>
-    <row r="157" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>156</v>
       </c>
@@ -11860,7 +11872,7 @@
       </c>
       <c r="M157"/>
     </row>
-    <row r="158" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>157</v>
       </c>
@@ -11895,7 +11907,7 @@
       </c>
       <c r="M158"/>
     </row>
-    <row r="159" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>158</v>
       </c>
@@ -11932,7 +11944,7 @@
       </c>
       <c r="M159"/>
     </row>
-    <row r="160" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>159</v>
       </c>
@@ -11967,7 +11979,7 @@
       </c>
       <c r="M160"/>
     </row>
-    <row r="161" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>160</v>
       </c>
@@ -12002,7 +12014,7 @@
       </c>
       <c r="M161"/>
     </row>
-    <row r="162" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>161</v>
       </c>
@@ -12037,7 +12049,7 @@
       </c>
       <c r="M162"/>
     </row>
-    <row r="163" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>162</v>
       </c>
@@ -12072,7 +12084,7 @@
       </c>
       <c r="M163"/>
     </row>
-    <row r="164" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>163</v>
       </c>
@@ -12107,7 +12119,7 @@
       </c>
       <c r="M164"/>
     </row>
-    <row r="165" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>164</v>
       </c>
@@ -12142,7 +12154,7 @@
       </c>
       <c r="M165"/>
     </row>
-    <row r="166" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>165</v>
       </c>
@@ -12179,7 +12191,7 @@
       </c>
       <c r="M166"/>
     </row>
-    <row r="167" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>166</v>
       </c>
@@ -12214,7 +12226,7 @@
       </c>
       <c r="M167"/>
     </row>
-    <row r="168" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>167</v>
       </c>
@@ -12249,7 +12261,7 @@
       </c>
       <c r="M168"/>
     </row>
-    <row r="169" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>168</v>
       </c>
@@ -12284,7 +12296,7 @@
       </c>
       <c r="M169"/>
     </row>
-    <row r="170" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>169</v>
       </c>
@@ -12319,7 +12331,7 @@
       </c>
       <c r="M170"/>
     </row>
-    <row r="171" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>170</v>
       </c>
@@ -12356,7 +12368,7 @@
       </c>
       <c r="M171"/>
     </row>
-    <row r="172" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>171</v>
       </c>
@@ -12391,7 +12403,7 @@
       </c>
       <c r="M172"/>
     </row>
-    <row r="173" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>172</v>
       </c>
@@ -12426,7 +12438,7 @@
       </c>
       <c r="M173"/>
     </row>
-    <row r="174" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>173</v>
       </c>
@@ -12461,7 +12473,7 @@
       </c>
       <c r="M174"/>
     </row>
-    <row r="175" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>174</v>
       </c>
@@ -12498,7 +12510,7 @@
       </c>
       <c r="M175"/>
     </row>
-    <row r="176" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>175</v>
       </c>
@@ -12533,7 +12545,7 @@
       </c>
       <c r="M176"/>
     </row>
-    <row r="177" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>176</v>
       </c>
@@ -12570,7 +12582,7 @@
       </c>
       <c r="M177"/>
     </row>
-    <row r="178" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>177</v>
       </c>
@@ -12607,7 +12619,7 @@
       </c>
       <c r="M178"/>
     </row>
-    <row r="179" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>178</v>
       </c>
@@ -12642,7 +12654,7 @@
       </c>
       <c r="M179"/>
     </row>
-    <row r="180" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>179</v>
       </c>
@@ -12677,7 +12689,7 @@
       </c>
       <c r="M180"/>
     </row>
-    <row r="181" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>180</v>
       </c>
@@ -12712,7 +12724,7 @@
       </c>
       <c r="M181"/>
     </row>
-    <row r="182" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>181</v>
       </c>
@@ -12749,7 +12761,7 @@
       </c>
       <c r="M182"/>
     </row>
-    <row r="183" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>182</v>
       </c>
@@ -12784,7 +12796,7 @@
       </c>
       <c r="M183"/>
     </row>
-    <row r="184" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>183</v>
       </c>
@@ -12819,7 +12831,7 @@
       </c>
       <c r="M184"/>
     </row>
-    <row r="185" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>184</v>
       </c>
@@ -12854,7 +12866,7 @@
       </c>
       <c r="M185"/>
     </row>
-    <row r="186" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>185</v>
       </c>
@@ -12891,7 +12903,7 @@
       </c>
       <c r="M186"/>
     </row>
-    <row r="187" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>186</v>
       </c>
@@ -12926,7 +12938,7 @@
       </c>
       <c r="M187"/>
     </row>
-    <row r="188" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>187</v>
       </c>
@@ -12961,7 +12973,7 @@
       </c>
       <c r="M188"/>
     </row>
-    <row r="189" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>188</v>
       </c>
@@ -12998,7 +13010,7 @@
       </c>
       <c r="M189"/>
     </row>
-    <row r="190" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>189</v>
       </c>
@@ -13033,7 +13045,7 @@
       </c>
       <c r="M190"/>
     </row>
-    <row r="191" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>190</v>
       </c>
@@ -13068,7 +13080,7 @@
       </c>
       <c r="M191"/>
     </row>
-    <row r="192" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>191</v>
       </c>
@@ -13103,7 +13115,7 @@
       </c>
       <c r="M192"/>
     </row>
-    <row r="193" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>192</v>
       </c>
@@ -13140,7 +13152,7 @@
       </c>
       <c r="M193"/>
     </row>
-    <row r="194" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>193</v>
       </c>
@@ -13175,7 +13187,7 @@
       </c>
       <c r="M194"/>
     </row>
-    <row r="195" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>194</v>
       </c>
@@ -13210,7 +13222,7 @@
       </c>
       <c r="M195"/>
     </row>
-    <row r="196" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>195</v>
       </c>
@@ -13247,7 +13259,7 @@
       </c>
       <c r="M196"/>
     </row>
-    <row r="197" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>196</v>
       </c>
@@ -13284,7 +13296,7 @@
       </c>
       <c r="M197"/>
     </row>
-    <row r="198" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>197</v>
       </c>
@@ -13321,7 +13333,7 @@
       </c>
       <c r="M198"/>
     </row>
-    <row r="199" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>198</v>
       </c>
@@ -13356,7 +13368,7 @@
       </c>
       <c r="M199"/>
     </row>
-    <row r="200" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>199</v>
       </c>
@@ -13393,7 +13405,7 @@
       </c>
       <c r="M200"/>
     </row>
-    <row r="201" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>200</v>
       </c>
@@ -13428,7 +13440,7 @@
       </c>
       <c r="M201"/>
     </row>
-    <row r="202" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>201</v>
       </c>
@@ -13465,7 +13477,7 @@
       </c>
       <c r="M202"/>
     </row>
-    <row r="203" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>202</v>
       </c>
@@ -13500,7 +13512,7 @@
       </c>
       <c r="M203"/>
     </row>
-    <row r="204" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>203</v>
       </c>
@@ -13535,7 +13547,7 @@
       </c>
       <c r="M204"/>
     </row>
-    <row r="205" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>204</v>
       </c>
@@ -13570,7 +13582,7 @@
       </c>
       <c r="M205"/>
     </row>
-    <row r="206" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>205</v>
       </c>
@@ -13605,7 +13617,7 @@
       </c>
       <c r="M206"/>
     </row>
-    <row r="207" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>206</v>
       </c>
@@ -13640,7 +13652,7 @@
       </c>
       <c r="M207"/>
     </row>
-    <row r="208" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>207</v>
       </c>
@@ -13675,7 +13687,7 @@
       </c>
       <c r="M208"/>
     </row>
-    <row r="209" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>208</v>
       </c>
@@ -13710,7 +13722,7 @@
       </c>
       <c r="M209"/>
     </row>
-    <row r="210" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>209</v>
       </c>
@@ -13747,7 +13759,7 @@
       </c>
       <c r="M210"/>
     </row>
-    <row r="211" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>210</v>
       </c>
@@ -13782,7 +13794,7 @@
       </c>
       <c r="M211"/>
     </row>
-    <row r="212" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>211</v>
       </c>
@@ -13819,7 +13831,7 @@
       </c>
       <c r="M212"/>
     </row>
-    <row r="213" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>212</v>
       </c>
@@ -13854,7 +13866,7 @@
       </c>
       <c r="M213"/>
     </row>
-    <row r="214" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>213</v>
       </c>
@@ -13889,7 +13901,7 @@
       </c>
       <c r="M214"/>
     </row>
-    <row r="215" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>214</v>
       </c>
@@ -13924,7 +13936,7 @@
       </c>
       <c r="M215"/>
     </row>
-    <row r="216" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>215</v>
       </c>
@@ -13961,7 +13973,7 @@
       </c>
       <c r="M216"/>
     </row>
-    <row r="217" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>216</v>
       </c>
@@ -13998,7 +14010,7 @@
       </c>
       <c r="M217"/>
     </row>
-    <row r="218" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>217</v>
       </c>
@@ -14035,7 +14047,7 @@
       </c>
       <c r="M218"/>
     </row>
-    <row r="219" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>218</v>
       </c>
@@ -14070,7 +14082,7 @@
       </c>
       <c r="M219"/>
     </row>
-    <row r="220" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>219</v>
       </c>
@@ -14107,7 +14119,7 @@
       </c>
       <c r="M220"/>
     </row>
-    <row r="221" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>220</v>
       </c>
@@ -14144,7 +14156,7 @@
       </c>
       <c r="M221"/>
     </row>
-    <row r="222" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>221</v>
       </c>
@@ -14179,7 +14191,7 @@
       </c>
       <c r="M222"/>
     </row>
-    <row r="223" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>222</v>
       </c>
@@ -14214,7 +14226,7 @@
       </c>
       <c r="M223"/>
     </row>
-    <row r="224" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>223</v>
       </c>
@@ -14249,7 +14261,7 @@
       </c>
       <c r="M224"/>
     </row>
-    <row r="225" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>224</v>
       </c>
@@ -14288,7 +14300,7 @@
       </c>
       <c r="M225"/>
     </row>
-    <row r="226" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>225</v>
       </c>
@@ -14325,7 +14337,7 @@
       </c>
       <c r="M226"/>
     </row>
-    <row r="227" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>226</v>
       </c>
@@ -14362,7 +14374,7 @@
       </c>
       <c r="M227"/>
     </row>
-    <row r="228" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>227</v>
       </c>
@@ -14399,7 +14411,7 @@
       </c>
       <c r="M228"/>
     </row>
-    <row r="229" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" ht="330" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>228</v>
       </c>
@@ -14434,7 +14446,7 @@
       </c>
       <c r="M229"/>
     </row>
-    <row r="230" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>229</v>
       </c>
@@ -14469,7 +14481,7 @@
       </c>
       <c r="M230"/>
     </row>
-    <row r="231" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>230</v>
       </c>
@@ -14504,7 +14516,7 @@
       </c>
       <c r="M231"/>
     </row>
-    <row r="232" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>231</v>
       </c>
@@ -14541,7 +14553,7 @@
       </c>
       <c r="M232"/>
     </row>
-    <row r="233" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>232</v>
       </c>
@@ -14576,7 +14588,7 @@
       </c>
       <c r="M233"/>
     </row>
-    <row r="234" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>233</v>
       </c>
@@ -14611,7 +14623,7 @@
       </c>
       <c r="M234"/>
     </row>
-    <row r="235" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>234</v>
       </c>
@@ -14646,7 +14658,7 @@
       </c>
       <c r="M235"/>
     </row>
-    <row r="236" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>235</v>
       </c>
@@ -14681,7 +14693,7 @@
       </c>
       <c r="M236"/>
     </row>
-    <row r="237" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>236</v>
       </c>
@@ -14716,7 +14728,7 @@
       </c>
       <c r="M237"/>
     </row>
-    <row r="238" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>237</v>
       </c>
@@ -14751,7 +14763,7 @@
       </c>
       <c r="M238"/>
     </row>
-    <row r="239" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>238</v>
       </c>
@@ -14786,7 +14798,7 @@
       </c>
       <c r="M239"/>
     </row>
-    <row r="240" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>239</v>
       </c>
@@ -14821,7 +14833,7 @@
       </c>
       <c r="M240"/>
     </row>
-    <row r="241" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A241" s="6">
         <v>240</v>
       </c>
@@ -14856,7 +14868,7 @@
       </c>
       <c r="M241"/>
     </row>
-    <row r="242" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A242" s="6">
         <v>241</v>
       </c>
@@ -14893,7 +14905,7 @@
       </c>
       <c r="M242"/>
     </row>
-    <row r="243" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A243" s="6">
         <v>242</v>
       </c>
@@ -14928,7 +14940,7 @@
       </c>
       <c r="M243"/>
     </row>
-    <row r="244" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A244" s="6">
         <v>243</v>
       </c>
@@ -14963,7 +14975,7 @@
       </c>
       <c r="M244"/>
     </row>
-    <row r="245" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
         <v>244</v>
       </c>
@@ -14998,7 +15010,7 @@
       </c>
       <c r="M245"/>
     </row>
-    <row r="246" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A246" s="6">
         <v>245</v>
       </c>
@@ -15033,7 +15045,7 @@
       </c>
       <c r="M246"/>
     </row>
-    <row r="247" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A247" s="6">
         <v>246</v>
       </c>
@@ -15070,7 +15082,7 @@
       </c>
       <c r="M247"/>
     </row>
-    <row r="248" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>247</v>
       </c>
@@ -15105,7 +15117,7 @@
       </c>
       <c r="M248"/>
     </row>
-    <row r="249" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A249" s="6">
         <v>248</v>
       </c>
@@ -15140,7 +15152,7 @@
       </c>
       <c r="M249"/>
     </row>
-    <row r="250" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>249</v>
       </c>
@@ -15175,7 +15187,7 @@
       </c>
       <c r="M250"/>
     </row>
-    <row r="251" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
         <v>250</v>
       </c>
@@ -15210,7 +15222,7 @@
       </c>
       <c r="M251"/>
     </row>
-    <row r="252" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>251</v>
       </c>
@@ -15247,7 +15259,7 @@
       </c>
       <c r="M252"/>
     </row>
-    <row r="253" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A253" s="6">
         <v>252</v>
       </c>
@@ -15282,7 +15294,7 @@
       </c>
       <c r="M253"/>
     </row>
-    <row r="254" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A254" s="6">
         <v>253</v>
       </c>
@@ -15317,7 +15329,7 @@
       </c>
       <c r="M254"/>
     </row>
-    <row r="255" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A255" s="6">
         <v>254</v>
       </c>
@@ -15352,7 +15364,7 @@
       </c>
       <c r="M255"/>
     </row>
-    <row r="256" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A256" s="6">
         <v>255</v>
       </c>
@@ -15387,7 +15399,7 @@
       </c>
       <c r="M256"/>
     </row>
-    <row r="257" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A257" s="6">
         <v>256</v>
       </c>
@@ -15422,7 +15434,7 @@
       </c>
       <c r="M257"/>
     </row>
-    <row r="258" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A258" s="6">
         <v>257</v>
       </c>
@@ -15457,7 +15469,7 @@
       </c>
       <c r="M258"/>
     </row>
-    <row r="259" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A259" s="6">
         <v>258</v>
       </c>
@@ -15492,7 +15504,7 @@
       </c>
       <c r="M259"/>
     </row>
-    <row r="260" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A260" s="6">
         <v>259</v>
       </c>
@@ -15529,7 +15541,7 @@
       </c>
       <c r="M260"/>
     </row>
-    <row r="261" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A261" s="6">
         <v>260</v>
       </c>
@@ -15564,7 +15576,7 @@
       </c>
       <c r="M261"/>
     </row>
-    <row r="262" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A262" s="6">
         <v>261</v>
       </c>
@@ -15599,7 +15611,7 @@
       </c>
       <c r="M262"/>
     </row>
-    <row r="263" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A263" s="6">
         <v>262</v>
       </c>
@@ -15634,7 +15646,7 @@
       </c>
       <c r="M263"/>
     </row>
-    <row r="264" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A264" s="6">
         <v>263</v>
       </c>
@@ -15671,7 +15683,7 @@
       </c>
       <c r="M264"/>
     </row>
-    <row r="265" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A265" s="6">
         <v>264</v>
       </c>
@@ -15706,7 +15718,7 @@
       </c>
       <c r="M265"/>
     </row>
-    <row r="266" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A266" s="6">
         <v>265</v>
       </c>
@@ -15741,7 +15753,7 @@
       </c>
       <c r="M266"/>
     </row>
-    <row r="267" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A267" s="6">
         <v>266</v>
       </c>
@@ -15776,7 +15788,7 @@
       </c>
       <c r="M267"/>
     </row>
-    <row r="268" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A268" s="6">
         <v>267</v>
       </c>
@@ -15811,7 +15823,7 @@
       </c>
       <c r="M268"/>
     </row>
-    <row r="269" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A269" s="6">
         <v>268</v>
       </c>
@@ -15848,7 +15860,7 @@
       </c>
       <c r="M269"/>
     </row>
-    <row r="270" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A270" s="6">
         <v>269</v>
       </c>
@@ -15883,7 +15895,7 @@
       </c>
       <c r="M270"/>
     </row>
-    <row r="271" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A271" s="6">
         <v>270</v>
       </c>
@@ -15918,7 +15930,7 @@
       </c>
       <c r="M271"/>
     </row>
-    <row r="272" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A272" s="6">
         <v>271</v>
       </c>
@@ -15955,7 +15967,7 @@
       </c>
       <c r="M272"/>
     </row>
-    <row r="273" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A273" s="6">
         <v>272</v>
       </c>
@@ -15990,7 +16002,7 @@
       </c>
       <c r="M273"/>
     </row>
-    <row r="274" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A274" s="6">
         <v>273</v>
       </c>
@@ -16025,7 +16037,7 @@
       </c>
       <c r="M274"/>
     </row>
-    <row r="275" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A275" s="6">
         <v>274</v>
       </c>
@@ -16060,7 +16072,7 @@
       </c>
       <c r="M275"/>
     </row>
-    <row r="276" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A276" s="6">
         <v>275</v>
       </c>
@@ -16097,7 +16109,7 @@
       </c>
       <c r="M276"/>
     </row>
-    <row r="277" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A277" s="6">
         <v>276</v>
       </c>
@@ -16132,7 +16144,7 @@
       </c>
       <c r="M277"/>
     </row>
-    <row r="278" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A278" s="6">
         <v>277</v>
       </c>
@@ -16167,7 +16179,7 @@
       </c>
       <c r="M278"/>
     </row>
-    <row r="279" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A279" s="6">
         <v>278</v>
       </c>
@@ -16202,7 +16214,7 @@
       </c>
       <c r="M279"/>
     </row>
-    <row r="280" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A280" s="6">
         <v>279</v>
       </c>
@@ -16239,7 +16251,7 @@
       </c>
       <c r="M280"/>
     </row>
-    <row r="281" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A281" s="6">
         <v>280</v>
       </c>
@@ -16274,7 +16286,7 @@
       </c>
       <c r="M281"/>
     </row>
-    <row r="282" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A282" s="6">
         <v>281</v>
       </c>
@@ -16311,7 +16323,7 @@
       </c>
       <c r="M282"/>
     </row>
-    <row r="283" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A283" s="6">
         <v>282</v>
       </c>
@@ -16346,7 +16358,7 @@
       </c>
       <c r="M283"/>
     </row>
-    <row r="284" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A284" s="6">
         <v>283</v>
       </c>
@@ -16383,7 +16395,7 @@
       </c>
       <c r="M284"/>
     </row>
-    <row r="285" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A285" s="6">
         <v>284</v>
       </c>
@@ -16418,7 +16430,7 @@
       </c>
       <c r="M285"/>
     </row>
-    <row r="286" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A286" s="6">
         <v>285</v>
       </c>
@@ -16453,7 +16465,7 @@
       </c>
       <c r="M286"/>
     </row>
-    <row r="287" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A287" s="6">
         <v>286</v>
       </c>
@@ -16488,7 +16500,7 @@
       </c>
       <c r="M287"/>
     </row>
-    <row r="288" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A288" s="6">
         <v>287</v>
       </c>
@@ -16523,7 +16535,7 @@
       </c>
       <c r="M288"/>
     </row>
-    <row r="289" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A289" s="6">
         <v>288</v>
       </c>
@@ -16558,7 +16570,7 @@
       </c>
       <c r="M289"/>
     </row>
-    <row r="290" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A290" s="6">
         <v>289</v>
       </c>
@@ -16593,7 +16605,7 @@
       </c>
       <c r="M290"/>
     </row>
-    <row r="291" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A291" s="6">
         <v>290</v>
       </c>
@@ -16628,7 +16640,7 @@
       </c>
       <c r="M291"/>
     </row>
-    <row r="292" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A292" s="6">
         <v>291</v>
       </c>
@@ -16665,7 +16677,7 @@
       </c>
       <c r="M292"/>
     </row>
-    <row r="293" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A293" s="6">
         <v>292</v>
       </c>
@@ -16702,7 +16714,7 @@
       </c>
       <c r="M293"/>
     </row>
-    <row r="294" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A294" s="6">
         <v>293</v>
       </c>
@@ -16737,7 +16749,7 @@
       </c>
       <c r="M294"/>
     </row>
-    <row r="295" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A295" s="6">
         <v>294</v>
       </c>
@@ -16772,7 +16784,7 @@
       </c>
       <c r="M295"/>
     </row>
-    <row r="296" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A296" s="6">
         <v>295</v>
       </c>
@@ -16805,7 +16817,7 @@
       </c>
       <c r="M296"/>
     </row>
-    <row r="297" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A297" s="6">
         <v>296</v>
       </c>
@@ -16838,7 +16850,7 @@
       </c>
       <c r="M297"/>
     </row>
-    <row r="298" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A298" s="6">
         <v>297</v>
       </c>
@@ -16871,7 +16883,7 @@
       </c>
       <c r="M298"/>
     </row>
-    <row r="299" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A299" s="6">
         <v>298</v>
       </c>
@@ -16904,7 +16916,7 @@
       </c>
       <c r="M299"/>
     </row>
-    <row r="300" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A300" s="6">
         <v>299</v>
       </c>
@@ -16937,7 +16949,7 @@
       </c>
       <c r="M300"/>
     </row>
-    <row r="301" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A301" s="6">
         <v>300</v>
       </c>
@@ -16970,7 +16982,7 @@
       </c>
       <c r="M301"/>
     </row>
-    <row r="302" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A302" s="6">
         <v>301</v>
       </c>
@@ -17003,7 +17015,7 @@
       </c>
       <c r="M302"/>
     </row>
-    <row r="303" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A303" s="6">
         <v>302</v>
       </c>
@@ -17036,7 +17048,7 @@
       </c>
       <c r="M303"/>
     </row>
-    <row r="304" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A304" s="6">
         <v>303</v>
       </c>
@@ -17060,7 +17072,7 @@
       </c>
       <c r="M304"/>
     </row>
-    <row r="305" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A305" s="6">
         <v>304</v>
       </c>
@@ -17084,7 +17096,7 @@
       </c>
       <c r="M305"/>
     </row>
-    <row r="306" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A306" s="6">
         <v>305</v>
       </c>
@@ -17108,7 +17120,7 @@
       </c>
       <c r="M306"/>
     </row>
-    <row r="307" spans="1:13" ht="285" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:13" ht="285" x14ac:dyDescent="0.25">
       <c r="A307" s="6">
         <v>306</v>
       </c>
@@ -17132,7 +17144,7 @@
       </c>
       <c r="M307"/>
     </row>
-    <row r="308" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A308" s="6">
         <v>307</v>
       </c>
@@ -17153,7 +17165,7 @@
       </c>
       <c r="M308"/>
     </row>
-    <row r="309" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A309" s="6">
         <v>308</v>
       </c>
@@ -17177,7 +17189,7 @@
       </c>
       <c r="M309"/>
     </row>
-    <row r="310" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A310" s="6">
         <v>309</v>
       </c>
@@ -17201,7 +17213,7 @@
       </c>
       <c r="M310"/>
     </row>
-    <row r="311" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A311" s="6">
         <v>310</v>
       </c>
@@ -17225,7 +17237,7 @@
       </c>
       <c r="M311"/>
     </row>
-    <row r="312" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A312" s="6">
         <v>311</v>
       </c>
@@ -17249,7 +17261,7 @@
       </c>
       <c r="M312"/>
     </row>
-    <row r="313" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A313" s="6">
         <v>312</v>
       </c>
@@ -17273,7 +17285,7 @@
       </c>
       <c r="M313"/>
     </row>
-    <row r="314" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A314" s="6">
         <v>313</v>
       </c>
@@ -17294,7 +17306,7 @@
       </c>
       <c r="M314"/>
     </row>
-    <row r="315" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A315" s="6">
         <v>314</v>
       </c>
@@ -17318,7 +17330,7 @@
       </c>
       <c r="M315"/>
     </row>
-    <row r="316" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A316" s="6">
         <v>315</v>
       </c>
@@ -17342,7 +17354,7 @@
       </c>
       <c r="M316"/>
     </row>
-    <row r="317" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A317" s="6">
         <v>316</v>
       </c>
@@ -17363,7 +17375,7 @@
       </c>
       <c r="M317"/>
     </row>
-    <row r="318" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A318" s="6">
         <v>317</v>
       </c>
@@ -17387,7 +17399,7 @@
       </c>
       <c r="M318"/>
     </row>
-    <row r="319" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A319" s="6">
         <v>318</v>
       </c>
@@ -17408,7 +17420,7 @@
       </c>
       <c r="M319"/>
     </row>
-    <row r="320" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A320" s="6">
         <v>319</v>
       </c>
@@ -17429,7 +17441,7 @@
       </c>
       <c r="M320"/>
     </row>
-    <row r="321" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A321" s="6">
         <v>320</v>
       </c>
@@ -17453,7 +17465,7 @@
       </c>
       <c r="M321"/>
     </row>
-    <row r="322" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A322" s="6">
         <v>321</v>
       </c>
@@ -17474,7 +17486,7 @@
       </c>
       <c r="M322"/>
     </row>
-    <row r="323" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A323" s="6">
         <v>322</v>
       </c>
@@ -17498,7 +17510,7 @@
       </c>
       <c r="M323"/>
     </row>
-    <row r="324" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A324" s="6">
         <v>323</v>
       </c>
@@ -17519,7 +17531,7 @@
       </c>
       <c r="M324"/>
     </row>
-    <row r="325" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A325" s="6">
         <v>324</v>
       </c>
@@ -17540,7 +17552,7 @@
       </c>
       <c r="M325"/>
     </row>
-    <row r="326" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A326" s="6">
         <v>325</v>
       </c>
@@ -17561,7 +17573,7 @@
       </c>
       <c r="M326"/>
     </row>
-    <row r="327" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A327" s="6">
         <v>326</v>
       </c>
@@ -17582,7 +17594,7 @@
       </c>
       <c r="M327"/>
     </row>
-    <row r="328" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A328" s="6">
         <v>327</v>
       </c>
@@ -17603,7 +17615,7 @@
       </c>
       <c r="M328"/>
     </row>
-    <row r="329" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A329" s="6">
         <v>328</v>
       </c>
@@ -17624,7 +17636,7 @@
       </c>
       <c r="M329"/>
     </row>
-    <row r="330" spans="1:13" ht="285" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" ht="285" x14ac:dyDescent="0.25">
       <c r="A330" s="6">
         <v>329</v>
       </c>
@@ -17648,7 +17660,7 @@
       </c>
       <c r="M330"/>
     </row>
-    <row r="331" spans="1:13" ht="300" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" ht="300" x14ac:dyDescent="0.25">
       <c r="A331" s="6">
         <v>330</v>
       </c>
@@ -17672,7 +17684,7 @@
       </c>
       <c r="M331"/>
     </row>
-    <row r="332" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A332" s="6">
         <v>331</v>
       </c>
@@ -17693,7 +17705,7 @@
       </c>
       <c r="M332"/>
     </row>
-    <row r="333" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A333" s="6">
         <v>332</v>
       </c>
@@ -17714,7 +17726,7 @@
       </c>
       <c r="M333"/>
     </row>
-    <row r="334" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A334" s="6">
         <v>333</v>
       </c>
@@ -17735,7 +17747,7 @@
       </c>
       <c r="M334"/>
     </row>
-    <row r="335" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A335" s="6">
         <v>334</v>
       </c>
@@ -17756,7 +17768,7 @@
       </c>
       <c r="M335"/>
     </row>
-    <row r="336" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A336" s="6">
         <v>335</v>
       </c>
@@ -17777,7 +17789,7 @@
       </c>
       <c r="M336"/>
     </row>
-    <row r="337" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A337" s="6">
         <v>336</v>
       </c>
@@ -17798,7 +17810,7 @@
       </c>
       <c r="M337"/>
     </row>
-    <row r="338" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A338" s="6">
         <v>337</v>
       </c>
@@ -17819,7 +17831,7 @@
       </c>
       <c r="M338"/>
     </row>
-    <row r="339" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A339" s="6">
         <v>338</v>
       </c>
@@ -17840,7 +17852,7 @@
       </c>
       <c r="M339"/>
     </row>
-    <row r="340" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A340" s="6">
         <v>339</v>
       </c>
@@ -17864,7 +17876,7 @@
       </c>
       <c r="M340"/>
     </row>
-    <row r="341" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A341" s="6">
         <v>340</v>
       </c>
@@ -17888,7 +17900,7 @@
       </c>
       <c r="M341"/>
     </row>
-    <row r="342" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A342" s="6">
         <v>341</v>
       </c>
@@ -17912,7 +17924,7 @@
       </c>
       <c r="M342"/>
     </row>
-    <row r="343" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A343" s="6">
         <v>342</v>
       </c>
@@ -17936,7 +17948,7 @@
       </c>
       <c r="M343"/>
     </row>
-    <row r="344" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A344" s="6">
         <v>343</v>
       </c>
@@ -17957,7 +17969,7 @@
       </c>
       <c r="M344"/>
     </row>
-    <row r="345" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A345" s="6">
         <v>344</v>
       </c>
@@ -17978,7 +17990,7 @@
       </c>
       <c r="M345"/>
     </row>
-    <row r="346" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A346" s="6">
         <v>345</v>
       </c>
@@ -17999,7 +18011,7 @@
       </c>
       <c r="M346"/>
     </row>
-    <row r="347" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A347" s="6">
         <v>346</v>
       </c>
@@ -18020,7 +18032,7 @@
       </c>
       <c r="M347"/>
     </row>
-    <row r="348" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A348" s="6">
         <v>347</v>
       </c>
@@ -18044,7 +18056,7 @@
       </c>
       <c r="M348"/>
     </row>
-    <row r="349" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A349" s="6">
         <v>348</v>
       </c>
@@ -18068,7 +18080,7 @@
       </c>
       <c r="M349"/>
     </row>
-    <row r="350" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A350" s="6">
         <v>349</v>
       </c>
@@ -18092,7 +18104,7 @@
       </c>
       <c r="M350"/>
     </row>
-    <row r="351" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:13" ht="330" x14ac:dyDescent="0.25">
       <c r="A351" s="6">
         <v>350</v>
       </c>
@@ -19397,6 +19409,198 @@
       </c>
       <c r="L391" s="7" t="s">
         <v>1468</v>
+      </c>
+    </row>
+    <row r="392" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A392" s="6">
+        <v>600</v>
+      </c>
+      <c r="B392" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C392" s="7" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D392" s="7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E392" s="7" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F392" s="7" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G392" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="H392" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K392" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="L392" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="393" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A393" s="6">
+        <v>601</v>
+      </c>
+      <c r="B393" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C393" s="7" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D393" s="7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E393" s="7" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F393" s="7" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G393" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="H393" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K393" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="L393" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="394" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A394" s="6">
+        <v>602</v>
+      </c>
+      <c r="B394" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C394" s="7" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D394" s="7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E394" s="7" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F394" s="7" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G394" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="H394" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="K394" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="L394" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="395" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A395" s="6">
+        <v>603</v>
+      </c>
+      <c r="B395" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C395" s="7" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D395" s="7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E395" s="7" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F395" s="7" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G395" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="H395" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K395" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="L395" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="396" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A396" s="6">
+        <v>604</v>
+      </c>
+      <c r="B396" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C396" s="7" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D396" s="7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E396" s="7" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F396" s="7" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G396" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="H396" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K396" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="L396" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="397" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A397" s="6">
+        <v>605</v>
+      </c>
+      <c r="B397" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C397" s="7" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D397" s="7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E397" s="7" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F397" s="7" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G397" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="H397" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K397" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="L397" s="7" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -19419,15 +19623,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CBDF7B66595A64439AABDB96FE71B892" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="811f0579353e425b0025ec3edb8563e4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9aa45f56-20ac-4c96-9c8e-f70301df430f" xmlns:ns3="0d112806-a571-4b5c-9687-83175e2be7e0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f824535d616dc40657191cd3fbc597b" ns2:_="" ns3:_="">
     <xsd:import namespace="9aa45f56-20ac-4c96-9c8e-f70301df430f"/>
@@ -19656,6 +19851,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D191370-FA12-4ECA-BBBD-905F1A292662}">
   <ds:schemaRefs>
@@ -19668,14 +19872,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DA53B7A-809E-4CE1-85C5-B36B515ABA21}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DC14334-4C93-4754-A0EE-1688C9341C46}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19692,4 +19888,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DA53B7A-809E-4CE1-85C5-B36B515ABA21}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>